--- a/artfynd/A 24907-2026 artfynd.xlsx
+++ b/artfynd/A 24907-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>16506040</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>423511.4342265268</v>
+        <v>423511</v>
       </c>
       <c r="R2" t="n">
-        <v>6220471.49044247</v>
+        <v>6220471</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,19 +746,9 @@
           <t>2014-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63912982</v>
+        <v>134327825</v>
       </c>
       <c r="B3" t="n">
-        <v>110586</v>
+        <v>75354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,37 +791,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>6427</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>450m NV Frö korra, Sk</t>
+          <t>Rännarehusen NV, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424395</v>
+        <v>423465</v>
       </c>
       <c r="R3" t="n">
-        <v>6221367</v>
+        <v>6220496</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2002-04-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2002-04-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hedera helix var. helix/3D4e4443/Stoby s:n/KSd/ /Karin Strand,Sösdala</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,31 +862,953 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>på träd i blandskog</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>SkFlora    748557</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134327822</v>
+      </c>
+      <c r="B4" t="n">
+        <v>81031</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6444</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skriftlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Graphis scripta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rännarehusen NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>423465</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6220496</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134328062</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rännarehusen NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>423635</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6220527</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134327912</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98623</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220007</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Missne</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Calla palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rännarehusen NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>423559</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6220527</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134327948</v>
+      </c>
+      <c r="B7" t="n">
+        <v>111210</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rännarehusen NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>423605</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6220494</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Några avblommade ex Mycket svårt att avgöra antal pga övrig vegetation 300 ex enl inventering 2024</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134327985</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104878</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221178</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bäckbräsma</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cardamine amara</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rännarehusen NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>423605</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6220494</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134327857</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99857</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222308</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rankstarr</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carex elongata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rännarehusen NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>423559</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6220527</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134327818</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99960</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rännarehusen NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>423465</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6220496</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134327848</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rännarehusen NV, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>423559</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6220527</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>63912982</v>
+      </c>
+      <c r="B12" t="n">
+        <v>111175</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>450m NV Frö korra, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>424395</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6221367</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2002-04-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2002-04-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hedera helix var. helix/3D4e4443/Stoby s:n/KSd/ /Karin Strand,Sösdala</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>på träd i blandskog</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>SkFlora    748557</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Stefan Andersson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Karin Strand</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Skånes Flora (1989-2006)</t>
         </is>

--- a/artfynd/A 24907-2026 artfynd.xlsx
+++ b/artfynd/A 24907-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16506040</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134327825</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134327822</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134327818</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135041722</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135085781</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134328062</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135041716</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135041725</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135041726</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,6 +1949,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135085777</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2010,6 +2070,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135085783</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2124,6 +2189,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63912982</t>
         </is>
       </c>
     </row>
@@ -2228,6 +2298,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134327912</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2335,6 +2410,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134327948</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2437,6 +2517,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134327985</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2539,6 +2624,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134327857</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2641,8 +2731,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134327848</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24907-2026 artfynd.xlsx
+++ b/artfynd/A 24907-2026 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>135041722</v>
       </c>
       <c r="B6" t="n">
-        <v>58260</v>
+        <v>58265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135085781</v>
       </c>
       <c r="B7" t="n">
-        <v>58260</v>
+        <v>58265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135041716</v>
       </c>
       <c r="B9" t="n">
-        <v>58134</v>
+        <v>58139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>135041725</v>
       </c>
       <c r="B10" t="n">
-        <v>58134</v>
+        <v>58139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135041726</v>
       </c>
       <c r="B11" t="n">
-        <v>58134</v>
+        <v>58139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>135085777</v>
       </c>
       <c r="B12" t="n">
-        <v>58134</v>
+        <v>58139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>135085783</v>
       </c>
       <c r="B13" t="n">
-        <v>58134</v>
+        <v>58139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
